--- a/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="E2">
-        <v>17.5</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E3">
-        <v>19.3</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>11.1</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
-        <v>56.1</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>25.9</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
-        <v>1.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>35.7</v>
       </c>
       <c r="E6">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C8">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C4">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">
@@ -763,16 +763,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>70.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2">
-        <v>81.09999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="3">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4">
-        <v>28.2</v>
+        <v>26.2</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
     </row>
   </sheetData>

--- a/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
-        <v>10.3</v>
+        <v>3.6</v>
       </c>
       <c r="E2">
-        <v>16.2</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>5</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="E3">
-        <v>25.7</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>13.8</v>
+        <v>21.4</v>
       </c>
       <c r="E4">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
-        <v>24.1</v>
+        <v>21.4</v>
       </c>
       <c r="E5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="6">
@@ -472,13 +472,13 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="E6">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C7">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C8">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C4">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Tamil Nadu/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>3.6</v>
+        <v>12.2</v>
       </c>
       <c r="E2">
-        <v>21.1</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="3">
@@ -412,16 +412,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>17.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="E3">
-        <v>22.5</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>21.4</v>
+        <v>19.5</v>
       </c>
       <c r="E4">
-        <v>46.5</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>21.4</v>
+        <v>12.2</v>
       </c>
       <c r="E5">
-        <v>5.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6">
-        <v>35.7</v>
+        <v>46.3</v>
       </c>
       <c r="E6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="7">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C7">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C8">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C4">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -726,7 +726,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -772,39 +772,26 @@
         <v>75</v>
       </c>
       <c r="E2">
-        <v>83.3</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trend Different</t>
+          <t>IUCN</t>
         </is>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IUCN</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>26.2</v>
-      </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
-      <c r="E4">
-        <v>16.7</v>
+        <v>27.2</v>
+      </c>
+      <c r="D3">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>21.1</v>
       </c>
     </row>
   </sheetData>
